--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133664672</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>133664671</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133664672</v>
+        <v>133664671</v>
       </c>
       <c r="B2" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608833</v>
+        <v>608838</v>
       </c>
       <c r="R2" t="n">
-        <v>7006413</v>
+        <v>7006421</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133664671</v>
+        <v>133664672</v>
       </c>
       <c r="B3" t="n">
-        <v>80481</v>
+        <v>99195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608838</v>
+        <v>608833</v>
       </c>
       <c r="R3" t="n">
-        <v>7006421</v>
+        <v>7006413</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133664671</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133664672</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>